--- a/marketing_forms/012_email_campaign_plan_form_template--marketing_forms.xlsx
+++ b/marketing_forms/012_email_campaign_plan_form_template--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1275,8 +1275,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'segment_1'}</t>
+          <t>segment_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Segment 1'}</t>
+          <t>Segment 1</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'segment_2'}</t>
+          <t>segment_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Segment 2'}</t>
+          <t>Segment 2</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_31,_'name':_'email_1'}</t>
+          <t>email_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 31, 'name': 'Email 1'}</t>
+          <t>Email 1</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_32,_'name':_'email_2'}</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 32, 'name': 'Email 2'}</t>
+          <t>Email 2</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_33,_'name':_'email_3'}</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 33, 'name': 'Email 3'}</t>
+          <t>Email 3</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_34,_'name':_'email_4'}</t>
+          <t>email_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 34, 'name': 'Email 4'}</t>
+          <t>Email 4</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_35,_'name':_'email_5'}</t>
+          <t>email_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 35, 'name': 'Email 5'}</t>
+          <t>Email 5</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_36,_'name':_'email_6'}</t>
+          <t>email_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 36, 'name': 'Email 6'}</t>
+          <t>Email 6</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_37,_'name':_'email_7'}</t>
+          <t>email_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 37, 'name': 'Email 7'}</t>
+          <t>Email 7</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_38,_'name':_'email_8'}</t>
+          <t>email_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 38, 'name': 'Email 8'}</t>
+          <t>Email 8</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_39,_'name':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 39, 'name': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_41,_'name':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 41, 'name': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_42,_'name':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 42, 'name': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_43,_'name':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 43, 'name': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_44,_'name':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 44, 'name': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_45,_'name':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 45, 'name': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_46,_'name':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 46, 'name': 'LinkedIn'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_47,_'name':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 47, 'name': 'YouTube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_51,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 51, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_52,_'name':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 52, 'name': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_53,_'name':_'sms'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 53, 'name': 'SMS'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_54,_'name':_'email_2'}</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 54, 'name': 'Email 2'}</t>
+          <t>Email 2</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_55,_'name':_'social_media_2'}</t>
+          <t>social_media_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 55, 'name': 'Social Media 2'}</t>
+          <t>Social Media 2</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_56,_'name':_'sms_2'}</t>
+          <t>sms_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 56, 'name': 'SMS 2'}</t>
+          <t>SMS 2</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_57,_'name':_'email_3'}</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 57, 'name': 'Email 3'}</t>
+          <t>Email 3</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_58,_'name':_'social_media_3'}</t>
+          <t>social_media_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 58, 'name': 'Social Media 3'}</t>
+          <t>Social Media 3</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_59,_'name':_'sms_3'}</t>
+          <t>sms_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 59, 'name': 'SMS 3'}</t>
+          <t>SMS 3</t>
         </is>
       </c>
     </row>
